--- a/高層集合住宅案例整理.xlsx
+++ b/高層集合住宅案例整理.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="132">
   <si>
     <t>Case</t>
   </si>
@@ -127,12 +127,6 @@
     <t>放射狀陽台、地中海氣候、有機造型</t>
   </si>
   <si>
-    <t>The Bryant</t>
-  </si>
-  <si>
-    <t>極簡美學、細部設計、水磨石立面</t>
-  </si>
-  <si>
     <t>One Central Park</t>
   </si>
   <si>
@@ -157,18 +151,6 @@
     <t>峽谷景觀、複合機能、公共步道</t>
   </si>
   <si>
-    <t>Norra Tornen (Helix)</t>
-  </si>
-  <si>
-    <t>模組化堆疊、都市地標、預製單元</t>
-  </si>
-  <si>
-    <t>108 Leonard</t>
-  </si>
-  <si>
-    <t>歷史改造、古典與現代結合、豪華適居</t>
-  </si>
-  <si>
     <t>Haut</t>
   </si>
   <si>
@@ -184,15 +166,6 @@
     <t>空中天橋、高密度、社會住宅範式</t>
   </si>
   <si>
-    <t>Cumulus District</t>
-  </si>
-  <si>
-    <t>Los Angeles, USA</t>
-  </si>
-  <si>
-    <t>都市連結、空中露台、動態立面</t>
-  </si>
-  <si>
     <t>79 &amp; Park</t>
   </si>
   <si>
@@ -208,202 +181,229 @@
     <t>橫向堆疊、垂直社區、空間通透性</t>
   </si>
   <si>
-    <t>The Smile</t>
-  </si>
-  <si>
-    <t>弧形立面、不鏽鋼材質、採光優化</t>
-  </si>
-  <si>
-    <t>25 King</t>
-  </si>
-  <si>
-    <t>Brisbane, Australia</t>
-  </si>
-  <si>
-    <t>120*</t>
-  </si>
-  <si>
-    <t>CLT木構、辦公住宅混合、低碳建築</t>
-  </si>
-  <si>
-    <t>Tower Edition</t>
+    <t>The Silo</t>
+  </si>
+  <si>
+    <t>Copenhagen, Denmark</t>
+  </si>
+  <si>
+    <t>舊穀倉改造、粗獷鍍鋅外殼、都市更新</t>
+  </si>
+  <si>
+    <t>56 Leonard Street</t>
+  </si>
+  <si>
+    <t>疊疊樂積木、懸挑露台、結構美學地標</t>
+  </si>
+  <si>
+    <t>Agora Garden (陶朱隱園)</t>
+  </si>
+  <si>
+    <t>Taipei, Taiwan</t>
+  </si>
+  <si>
+    <t>螺旋扭轉結構、極致垂直森林、吸碳建築</t>
+  </si>
+  <si>
+    <t>Tour Bois-le-Prêtre</t>
+  </si>
+  <si>
+    <t>Paris, France</t>
+  </si>
+  <si>
+    <t>舊社宅低碳改造、冬日花園擴建、普立茲克獎策略</t>
+  </si>
+  <si>
+    <t>One Thousand Museum</t>
+  </si>
+  <si>
+    <t>Miami, USA</t>
+  </si>
+  <si>
+    <t>外骨骼流線結構、無柱室內空間、液態建築美學</t>
+  </si>
+  <si>
+    <t>Mirador Building</t>
+  </si>
+  <si>
+    <t>Madrid, Spain</t>
+  </si>
+  <si>
+    <t>垂直立體巨框、空中大廣場、多樣性社交單元</t>
+  </si>
+  <si>
+    <t>Mjøstårnet</t>
+  </si>
+  <si>
+    <t>Brumunddal, Norway</t>
+  </si>
+  <si>
+    <t>高層全木構造(CLT)、低碳永續、複合式住宅</t>
+  </si>
+  <si>
+    <t>SkyVille@Dawson</t>
+  </si>
+  <si>
+    <t>垂直村落概念、空中公共露臺、高密度社會住宅</t>
+  </si>
+  <si>
+    <t>Aqua Tower</t>
+  </si>
+  <si>
+    <t>Chicago, USA</t>
+  </si>
+  <si>
+    <t>波浪狀懸挑陽台、地形學立面、視線與遮陽優化</t>
+  </si>
+  <si>
+    <t>Sky Habitat</t>
+  </si>
+  <si>
+    <t>階梯式矩陣、空中連橋路徑、多層次水平綠化</t>
+  </si>
+  <si>
+    <t>Linked Hybrid</t>
+  </si>
+  <si>
+    <t>Beijing, China</t>
+  </si>
+  <si>
+    <t>環狀空中環廊、都市巨型結構、地熱能永續設計</t>
+  </si>
+  <si>
+    <t>Pixel</t>
+  </si>
+  <si>
+    <t>Abu Dhabi, UAE</t>
+  </si>
+  <si>
+    <t>像素化立面、滲透性中庭、陶瓷與混凝土混構</t>
+  </si>
+  <si>
+    <t>Sky-Terrace @ Dawson</t>
+  </si>
+  <si>
+    <t>預製模組化施工、垂直社群空間、通透框架美學</t>
+  </si>
+  <si>
+    <t>扭轉造型開發、基地限制回應、結構幾何美學</t>
+  </si>
+  <si>
+    <t>Newfoundland Tower</t>
+  </si>
+  <si>
+    <t>London, UK</t>
+  </si>
+  <si>
+    <t>斜交框架外骨骼、菱形立面分割、高性能帷幕</t>
+  </si>
+  <si>
+    <t>One United Park</t>
+  </si>
+  <si>
+    <t>Bucharest, Romania</t>
+  </si>
+  <si>
+    <t>垂直立體園林、公私領域界定、都市景觀縫合</t>
+  </si>
+  <si>
+    <t>Reflections Keppel Bay</t>
+  </si>
+  <si>
+    <t>弧形塔樓群、不對稱構圖、雙層表皮系統</t>
+  </si>
+  <si>
+    <t>King Toronto</t>
+  </si>
+  <si>
+    <t>Toronto, Canada</t>
+  </si>
+  <si>
+    <t>模組化像素堆疊、山嶺意象造型、整合式植栽牆</t>
+  </si>
+  <si>
+    <t>Grand Tower</t>
+  </si>
+  <si>
+    <t>Frankfurt, Germany</t>
+  </si>
+  <si>
+    <t>菱形陽台元素、流暢立面曲線、極致玻璃透明性</t>
+  </si>
+  <si>
+    <t>Duo Singapore</t>
+  </si>
+  <si>
+    <t>凹向弧形面、蜂窩狀遮陽、都市孔隙率研究</t>
+  </si>
+  <si>
+    <t>MahaNakhon</t>
+  </si>
+  <si>
+    <t>Bangkok, Thailand</t>
+  </si>
+  <si>
+    <t>像素化侵蝕、三維視覺動態、垂直公共機能</t>
+  </si>
+  <si>
+    <t>Eden Tower</t>
+  </si>
+  <si>
+    <t>垂直森林概念、通透玻璃轉角、都市生態介面</t>
+  </si>
+  <si>
+    <t>VIctoria Dockside</t>
+  </si>
+  <si>
+    <t>Hong Kong, China</t>
+  </si>
+  <si>
+    <t>石材工藝立面、混合用途高層、濱海景觀回應</t>
+  </si>
+  <si>
+    <t>Grand Parc G, H, I</t>
+  </si>
+  <si>
+    <t>Bordeaux, France</t>
+  </si>
+  <si>
+    <t>溫室陽台增建、社會住宅更新、空間擴張邏輯</t>
+  </si>
+  <si>
+    <t>140 West Street</t>
+  </si>
+  <si>
+    <t>157*</t>
+  </si>
+  <si>
+    <t>裝飾藝術改造、結構加固轉化、歷史紋理重構</t>
+  </si>
+  <si>
+    <t>Vertical Village</t>
+  </si>
+  <si>
+    <t>木構造混合、多樣化模組、垂直向都市擴散</t>
+  </si>
+  <si>
+    <t>Robinson Tower</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>視覺斷裂設計、空中花園平台、都市孔隙率探索</t>
+  </si>
+  <si>
+    <t>156*</t>
+  </si>
+  <si>
+    <t>垂直中庭、巨型都市相框、多樣性居住單元</t>
+  </si>
+  <si>
+    <t>Tour Total</t>
   </si>
   <si>
     <t>Berlin, Germany</t>
-  </si>
-  <si>
-    <t>簡約機能、都市縫合、預鑄美學</t>
-  </si>
-  <si>
-    <t>SkyVille@Dawson</t>
-  </si>
-  <si>
-    <t>垂直村落概念、空中公共露臺、高密度社會住宅</t>
-  </si>
-  <si>
-    <t>Aqua Tower</t>
-  </si>
-  <si>
-    <t>Chicago, USA</t>
-  </si>
-  <si>
-    <t>波浪狀懸挑陽台、地形學立面、視線與遮陽優化</t>
-  </si>
-  <si>
-    <t>Sky Habitat</t>
-  </si>
-  <si>
-    <t>階梯式矩陣、空中連橋路徑、多層次水平綠化</t>
-  </si>
-  <si>
-    <t>Linked Hybrid</t>
-  </si>
-  <si>
-    <t>Beijing, China</t>
-  </si>
-  <si>
-    <t>環狀空中環廊、都市巨型結構、地熱能永續設計</t>
-  </si>
-  <si>
-    <t>Pixel</t>
-  </si>
-  <si>
-    <t>Abu Dhabi, UAE</t>
-  </si>
-  <si>
-    <t>像素化立面、滲透性中庭、陶瓷與混凝土混構</t>
-  </si>
-  <si>
-    <t>Sky-Terrace @ Dawson</t>
-  </si>
-  <si>
-    <t>預製模組化施工、垂直社群空間、通透框架美學</t>
-  </si>
-  <si>
-    <t>扭轉造型開發、基地限制回應、結構幾何美學</t>
-  </si>
-  <si>
-    <t>Newfoundland Tower</t>
-  </si>
-  <si>
-    <t>London, UK</t>
-  </si>
-  <si>
-    <t>斜交框架外骨骼、菱形立面分割、高性能帷幕</t>
-  </si>
-  <si>
-    <t>One United Park</t>
-  </si>
-  <si>
-    <t>Bucharest, Romania</t>
-  </si>
-  <si>
-    <t>垂直立體園林、公私領域界定、都市景觀縫合</t>
-  </si>
-  <si>
-    <t>Reflections Keppel Bay</t>
-  </si>
-  <si>
-    <t>弧形塔樓群、不對稱構圖、雙層表皮系統</t>
-  </si>
-  <si>
-    <t>King Toronto</t>
-  </si>
-  <si>
-    <t>Toronto, Canada</t>
-  </si>
-  <si>
-    <t>模組化像素堆疊、山嶺意象造型、整合式植栽牆</t>
-  </si>
-  <si>
-    <t>Grand Tower</t>
-  </si>
-  <si>
-    <t>Frankfurt, Germany</t>
-  </si>
-  <si>
-    <t>菱形陽台元素、流暢立面曲線、極致玻璃透明性</t>
-  </si>
-  <si>
-    <t>Duo Singapore</t>
-  </si>
-  <si>
-    <t>凹向弧形面、蜂窩狀遮陽、都市孔隙率研究</t>
-  </si>
-  <si>
-    <t>MahaNakhon</t>
-  </si>
-  <si>
-    <t>Bangkok, Thailand</t>
-  </si>
-  <si>
-    <t>像素化侵蝕、三維視覺動態、垂直公共機能</t>
-  </si>
-  <si>
-    <t>Eden Tower</t>
-  </si>
-  <si>
-    <t>垂直森林概念、通透玻璃轉角、都市生態介面</t>
-  </si>
-  <si>
-    <t>VIctoria Dockside</t>
-  </si>
-  <si>
-    <t>Hong Kong, China</t>
-  </si>
-  <si>
-    <t>石材工藝立面、混合用途高層、濱海景觀回應</t>
-  </si>
-  <si>
-    <t>Grand Parc G, H, I</t>
-  </si>
-  <si>
-    <t>Bordeaux, France</t>
-  </si>
-  <si>
-    <t>溫室陽台增建、社會住宅更新、空間擴張邏輯</t>
-  </si>
-  <si>
-    <t>140 West Street</t>
-  </si>
-  <si>
-    <t>157*</t>
-  </si>
-  <si>
-    <t>裝飾藝術改造、結構加固轉化、歷史紋理重構</t>
-  </si>
-  <si>
-    <t>Vertical Village</t>
-  </si>
-  <si>
-    <t>Paris, France</t>
-  </si>
-  <si>
-    <t>木構造混合、多樣化模組、垂直向都市擴散</t>
-  </si>
-  <si>
-    <t>Robinson Tower</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>視覺斷裂設計、空中花園平台、都市孔隙率探索</t>
-  </si>
-  <si>
-    <t>Mirador Building</t>
-  </si>
-  <si>
-    <t>Madrid, Spain</t>
-  </si>
-  <si>
-    <t>156*</t>
-  </si>
-  <si>
-    <t>垂直中庭、巨型都市相框、多樣性居住單元</t>
-  </si>
-  <si>
-    <t>Tour Total</t>
   </si>
   <si>
     <t>立面摺紙邏輯、動態光影變化、純粹幾何重複</t>
@@ -413,10 +413,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -440,6 +437,11 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
   </fonts>
@@ -485,8 +487,8 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,6 +704,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -712,7 +715,7 @@
     <col customWidth="1" min="5" max="5" width="15.88"/>
     <col customWidth="1" min="6" max="6" width="9.88"/>
     <col customWidth="1" min="7" max="7" width="13.75"/>
-    <col customWidth="1" min="9" max="9" width="32.88"/>
+    <col customWidth="1" min="9" max="9" width="41.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -939,64 +942,64 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4">
-        <v>2021.0</v>
+        <v>2014.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4">
         <v>34.0</v>
       </c>
-      <c r="G9" s="4">
-        <v>57.0</v>
+      <c r="G9" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="H9" s="5">
-        <v>20000.0</v>
+        <v>67000.0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="4">
-        <v>2014.0</v>
+        <v>2021.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F10" s="4">
-        <v>34.0</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>21.0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>198.0</v>
       </c>
       <c r="H10" s="5">
-        <v>67000.0</v>
+        <v>75000.0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="4">
-        <v>2021.0</v>
+        <v>2022.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
@@ -1005,10 +1008,10 @@
         <v>21.0</v>
       </c>
       <c r="G11" s="4">
-        <v>198.0</v>
+        <v>52.0</v>
       </c>
       <c r="H11" s="5">
-        <v>75000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>47</v>
@@ -1020,303 +1023,477 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4">
-        <v>2020.0</v>
+        <v>2009.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F12" s="4">
-        <v>33.0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>138.0</v>
+        <v>50.0</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="H12" s="5">
-        <v>15000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4">
-        <v>2020.0</v>
+        <v>2018.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F13" s="4">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="G13" s="4">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="H13" s="5">
-        <v>37000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="4">
-        <v>2022.0</v>
+        <v>2013.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="4">
+        <v>24.0</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="5">
+        <v>170000.0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>52.0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>14500.0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4">
-        <v>2009.0</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="F15" s="4">
-        <v>50.0</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>55</v>
+        <v>17.0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>38.0</v>
       </c>
       <c r="H15" s="5">
-        <v>150000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="3"/>
+      <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="C16" s="4">
-        <v>2020.0</v>
+        <v>2017.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="4">
-        <v>31.0</v>
+        <v>57.0</v>
       </c>
       <c r="G16" s="4">
-        <v>148.0</v>
+        <v>145.0</v>
       </c>
       <c r="H16" s="5">
-        <v>25000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="3"/>
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="C17" s="4">
         <v>2018.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>42300.0</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>169.0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>25000.0</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4">
-        <v>2013.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="F18" s="4">
-        <v>24.0</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>63</v>
+        <v>17.0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>96.0</v>
       </c>
       <c r="H18" s="5">
-        <v>170000.0</v>
+        <v>8900.0</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="3"/>
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="C19" s="4">
-        <v>2020.0</v>
+        <v>2019.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="7">
-        <v>46338.0</v>
+      <c r="F19" s="4">
+        <v>62.0</v>
       </c>
       <c r="G19" s="4">
-        <v>163.0</v>
+        <v>84.0</v>
       </c>
       <c r="H19" s="5">
-        <v>24000.0</v>
+        <v>84000.0</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="3"/>
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C20" s="4">
-        <v>2018.0</v>
+        <v>2005.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="7">
-        <v>46307.0</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>69</v>
+        <v>11</v>
+      </c>
+      <c r="F20" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>156.0</v>
       </c>
       <c r="H20" s="5">
-        <v>15000.0</v>
+        <v>18300.0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="3"/>
+      <c r="A21" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="C21" s="4">
-        <v>2022.0</v>
+        <v>2019.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="4">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G21" s="4">
-        <v>85.0</v>
+        <v>33.0</v>
       </c>
       <c r="H21" s="5">
-        <v>12000.0</v>
+        <v>11300.0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47">
-      <c r="E47" s="3"/>
+      <c r="A47" s="7"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48">
-      <c r="E48" s="3"/>
+      <c r="A48" s="7"/>
+      <c r="I48" s="3"/>
     </row>
     <row r="49">
-      <c r="E49" s="3"/>
+      <c r="A49" s="7"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50">
-      <c r="E50" s="3"/>
+      <c r="A50" s="7"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51">
-      <c r="E51" s="3"/>
+      <c r="A51" s="7"/>
+      <c r="I51" s="3"/>
     </row>
     <row r="52">
-      <c r="E52" s="3"/>
+      <c r="A52" s="7"/>
+      <c r="I52" s="3"/>
     </row>
     <row r="53">
-      <c r="E53" s="3"/>
+      <c r="A53" s="7"/>
+      <c r="I53" s="3"/>
     </row>
     <row r="54">
-      <c r="E54" s="3"/>
+      <c r="A54" s="7"/>
+      <c r="I54" s="3"/>
     </row>
     <row r="55">
-      <c r="E55" s="3"/>
+      <c r="A55" s="7"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56">
-      <c r="E56" s="3"/>
+      <c r="A56" s="7"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7"/>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="I64" s="3"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C66" s="4">
         <v>2015.0</v>
@@ -1337,18 +1514,18 @@
         <v>113900.0</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C67" s="4">
         <v>2009.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>16</v>
@@ -1363,12 +1540,12 @@
         <v>176500.0</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C68" s="4">
         <v>2015.0</v>
@@ -1389,18 +1566,18 @@
         <v>60000.0</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C69" s="4">
         <v>2009.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>21</v>
@@ -1415,18 +1592,18 @@
         <v>220000.0</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C70" s="4">
         <v>2024.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>21</v>
@@ -1441,12 +1618,12 @@
         <v>85000.0</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C71" s="4">
         <v>2015.0</v>
@@ -1467,7 +1644,7 @@
         <v>65000.0</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72">
@@ -1493,18 +1670,18 @@
         <v>60000.0</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C73" s="4">
         <v>2020.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>11</v>
@@ -1519,18 +1696,18 @@
         <v>60000.0</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C74" s="4">
         <v>2022.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>11</v>
@@ -1545,12 +1722,12 @@
         <v>52000.0</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C75" s="4">
         <v>2011.0</v>
@@ -1571,18 +1748,18 @@
         <v>193000.0</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C76" s="4">
         <v>2023.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>16</v>
@@ -1597,19 +1774,19 @@
         <v>55000.0</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="4">
         <v>2020.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>11</v>
@@ -1624,12 +1801,12 @@
         <v>44000.0</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C78" s="4">
         <v>2018.0</v>
@@ -1650,18 +1827,18 @@
         <v>285000.0</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C79" s="4">
         <v>2016.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>21</v>
@@ -1676,18 +1853,18 @@
         <v>135000.0</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C80" s="4">
         <v>2021.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>11</v>
@@ -1702,18 +1879,18 @@
         <v>20000.0</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C81" s="4">
         <v>2019.0</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>21</v>
@@ -1728,18 +1905,18 @@
         <v>280000.0</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C82" s="4">
         <v>2017.0</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>11</v>
@@ -1754,12 +1931,12 @@
         <v>68000.0</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C83" s="4">
         <v>2019.0</v>
@@ -1774,24 +1951,24 @@
         <v>32.0</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H83" s="4">
         <v>43000.0</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C84" s="4">
         <v>2021.0</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>11</v>
@@ -1806,12 +1983,12 @@
         <v>28200.0</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C85" s="4">
         <v>2019.0</v>
@@ -1826,24 +2003,24 @@
         <v>20.0</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H85" s="4">
         <v>24000.0</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C86" s="4">
         <v>2005.0</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>11</v>
@@ -1852,24 +2029,24 @@
         <v>21.0</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H86" s="4">
         <v>18300.0</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C87" s="4">
         <v>2012.0</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>11</v>
@@ -1932,6 +2109,9 @@
     <hyperlink r:id="rId41" ref="A86"/>
     <hyperlink r:id="rId42" ref="A87"/>
   </hyperlinks>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId43"/>
 </worksheet>
 </file>